--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_259_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_259_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M2" t="n">
         <v>10</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M3" t="n">
         <v>8</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1338,13 +1338,13 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X17" t="n">
         <v>3</v>
@@ -1531,10 +1531,10 @@
         <v>26</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2318,13 +2318,13 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X22" t="n">
         <v>10</v>
@@ -2710,13 +2710,13 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X24" t="n">
         <v>4</v>
@@ -3105,10 +3105,10 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X26" t="n">
         <v>2</v>
@@ -3494,13 +3494,13 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X28" t="n">
         <v>6</v>
@@ -3827,16 +3827,16 @@
         <v>131</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="X30" t="n">
         <v>39</v>
@@ -4298,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
         <v>1</v>
@@ -4494,10 +4494,10 @@
         <v>2</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X36" t="n">
         <v>4</v>
@@ -4880,7 +4880,7 @@
         <v>16</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
         <v>2</v>
@@ -5079,13 +5079,13 @@
         <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X39" t="n">
         <v>7</v>
@@ -5272,7 +5272,7 @@
         <v>5</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X41" t="n">
         <v>2</v>
@@ -6056,7 +6056,7 @@
         <v>12</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -6255,13 +6255,13 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X45" t="n">
         <v>8</v>
@@ -6588,16 +6588,16 @@
         <v>106</v>
       </c>
       <c r="T47" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U47" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X47" t="n">
         <v>38</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_259_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_259_EL.xlsx
@@ -674,10 +674,10 @@
         <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="O2" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="P2" t="n">
         <v>3</v>
@@ -692,20 +692,20 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>79.59</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>8</v>
       </c>
       <c r="N3" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="O3" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="P3" t="n">
         <v>6</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>79.17</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,10 +1347,10 @@
         <v>2</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -1543,14 +1543,14 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -2327,14 +2327,14 @@
         <v>6</v>
       </c>
       <c r="X22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y22" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -2363,18 +2363,18 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AJ22" t="n">
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
@@ -2719,10 +2719,10 @@
         <v>2</v>
       </c>
       <c r="X24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2752,25 +2752,25 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -3111,14 +3111,14 @@
         <v>3</v>
       </c>
       <c r="X26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3503,14 +3503,14 @@
         <v>2</v>
       </c>
       <c r="X28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -3839,14 +3839,14 @@
         <v>15</v>
       </c>
       <c r="X30" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="Y30" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3872,25 +3872,25 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK30" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4500,10 +4500,10 @@
         <v>2</v>
       </c>
       <c r="X36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -4892,14 +4892,14 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y38" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5088,14 +5088,14 @@
         <v>2</v>
       </c>
       <c r="X39" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y39" t="n">
         <v>7</v>
       </c>
-      <c r="Y39" t="n">
-        <v>9</v>
-      </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="AA39" t="n">
@@ -5284,14 +5284,14 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5480,14 +5480,14 @@
         <v>2</v>
       </c>
       <c r="X41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5872,14 +5872,14 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6068,10 +6068,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y44" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -6264,14 +6264,14 @@
         <v>1</v>
       </c>
       <c r="X45" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AA45" t="n">
@@ -6600,14 +6600,14 @@
         <v>8</v>
       </c>
       <c r="X47" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="Y47" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="AA47" t="n">
